--- a/Employee_Reports_wi48/Mohamed Mufaris Mohamed Jameel Q0532.xlsx
+++ b/Employee_Reports_wi48/Mohamed Mufaris Mohamed Jameel Q0532.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-58</v>
+        <v>-61</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-284</v>
+        <v>-287</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-402</v>
+        <v>-405</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -873,11 +873,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-479</v>
+        <v>-482</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1057,11 +1057,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1094,11 +1094,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1143,11 +1143,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1192,11 +1192,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1229,11 +1229,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1266,11 +1266,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
